--- a/题库/PY程序设计实验-模拟题1.xlsx
+++ b/题库/PY程序设计实验-模拟题1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -238,229 +238,33 @@
     <t>Prog1.3.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"># </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用数字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>组成所有每位数字都不相同的三位数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-digits = [1,2,3,4]
-for i in digits:
-    for j in digits:
-        for k in digits:
-            if i != j and j != k and i != k:
+    <t xml:space="preserve">           if i != j and j != k and i != k:
                 print(i*100 + j*10 + k)</t>
-    </r>
   </si>
   <si>
     <t>Prog1.4.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"># </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等腰三角形图案</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-for i in range(1,5):
-    # </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打印空格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    print(" "*(4-i), end="")
-    # </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打印星号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    for j in range(1, 2*i):
+    <t xml:space="preserve">    for j in range(1, 2*i):
         print("*", end="")
-    print()</t>
-    </r>
+    print("\n")</t>
   </si>
   <si>
     <t>Prog1.5.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"># </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等腰三角形（使用你提供的代码格式）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-for i in range(1,5):
-    for j in range(1, 2*i):
-        print("*", end="")
-    print()</t>
-    </r>
+    <t>for i in range(1,5):
+  for j in range(4-i):
+    print("",end="")
+  for j in range(1,2*i):
+    print("*",end=" ")
+  print("\n")</t>
   </si>
   <si>
     <t>Prog1.6.py</t>
   </si>
   <si>
-    <t>def Fibonacci(i):
-    if i == 1 or i == 2:
+    <t xml:space="preserve">    if i == 1 or i == 2:
         return 1
     else:
         return Fibonacci(i-1) + Fibonacci(i-2)</t>
@@ -469,7 +273,8 @@
     <t>Prog1.7.py</t>
   </si>
   <si>
-    <t xml:space="preserve">    for i in range(n):
+    <t>if 0&lt;a&lt;10:    
+    for i in range(n):
         ts = ts * 10 + a
         result += ts
     return result</t>
@@ -478,8 +283,7 @@
     <t>Prog1.8.py</t>
   </si>
   <si>
-    <t>squares = []
-for x in range(1, 11):
+    <t>for x in range(1, 11):
     squares.append(x ** 2)
     print(squares)</t>
   </si>
@@ -539,100 +343,11 @@
     <t>Prog1.10.py</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>while True:
-    x = int(input("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入整数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>x: "))
-    y = int(input("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入整数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>y: "))
-    op = input("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>输入运算符</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(+ - * /)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，其他退出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>: ")
-    if op not in ('+','-','*','/'):
-        break
-    if op == '+':
-        print(x + y)
-    elif op == '-':
-        print(x - y)
-    elif op == '*':
-        print(x * y)
-    elif op == '/':
-        print(x / y)</t>
-    </r>
+    <t>oper=('+','-','*','/')
+if op not in oper:
+    break
+dict1={'+':x+y,'-':x-y,'*':x*y,'/':x/y}
+print("{} {} {} = {}".format(x, op, y, dict1.get(op)))</t>
   </si>
 </sst>
 </file>
